--- a/Assets/Resources/DataBase/Review Data/ReviewDB.xlsx
+++ b/Assets/Resources/DataBase/Review Data/ReviewDB.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoYK\Documents\GitHub\Engine GenP 3D\LastDance\Assets\Resources\DataBase\Review Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Review Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C5783B-2C8A-40BC-B98F-A978D923BBF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1164" yWindow="3012" windowWidth="24096" windowHeight="14508"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReviewSheet" sheetId="1" r:id="rId1"/>
@@ -20,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
     </ext>
@@ -39,16 +29,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>content</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -110,13 +96,25 @@
   </si>
   <si>
     <t>여긴 참기름으로 기름 채우나베</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contentUp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contentDown1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contentDown2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -493,77 +491,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.08203125" customWidth="1"/>
+    <col min="5" max="5" width="38.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -573,43 +579,43 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataBase/Review Data/ReviewDB.xlsx
+++ b/Assets/Resources/DataBase/Review Data/ReviewDB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Review Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C5783B-2C8A-40BC-B98F-A978D923BBF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5083B132-3A1B-467A-A9E0-6C44B51ED86F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -47,22 +47,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>여기.주유소가.참.터가.좋네요.^^</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Gㅔㅁ마 T.브@이 주#유!소 폼 쩌네. 검색창에 검색 ㄱㄱ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>주유소에서 기름 냄새가 나요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>여기 기름값이 물보다 비쌀듯 ㅋㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -91,23 +79,111 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Late</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>여긴 참기름으로 기름 채우나베</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>contentUp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>contentDown1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>contentDown2</t>
+    <t>"시비거는 손님이 있어도 관리 하나도 안하는 주유소 "</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"진상의 정석이 있어도 진상 대응은 최악"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"너무 시끄럽고 무서워요..관리도 안하는 주유소"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"무료로 UFC를 볼 수 있는 최악의 주유소"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"정신병자. 날뛰는. 최악의. 주유소..."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contentDown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contentLate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여기.주유소가.참.조용하니.좋네요.^^</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주유소에서 기름 냄새가 나지만 청결합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"춤추기만 해도 뭐라하네요 완전 밤티"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여기 완전 개꿀야르한 주유소 꼭가세요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조용하고 분위기 완전 느좋 주유소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>손님 응대 GOAT 매가 약이다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사장님이 맛있고 기름이 친절해요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"사람들이 싸우는데 무섭고 사장은 말리지도 않음"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여기 기름값이 옆집 철수네보다 저렴하네요!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지연 정확 고급주유소..시간 없는데 너무 느림</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"대화도 못하게 하는 쓰레기 주유소!!"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기름값은 싸지만 손님 응대가 너무 느려요!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자판기 간식 전부 맛@도리임 안먹으면 인생 손해봐유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"자판기 이용하면 사장이 때리는 가게 가지마유"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여기는. 참기름으로. 기름. 채우나…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>손님 응대가 너무 느려유.. 자판기는 좋은데..아쉬워유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신속 정확 고급주유소 완벽하다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"주유하는 손님 때리는 미친 주유소임"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9만원에 가득채웠지만 또가고 싶은 GGM주유소 입니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -154,9 +230,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -492,12 +571,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.08203125" customWidth="1"/>
-    <col min="5" max="5" width="38.9140625" customWidth="1"/>
+    <col min="4" max="4" width="47" customWidth="1"/>
+    <col min="5" max="5" width="51.9140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -508,7 +587,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D1" t="s">
         <v>18</v>
@@ -521,55 +600,166 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>36</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>2</v>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>26</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>3</v>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>28</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>25</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -585,37 +775,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataBase/Review Data/ReviewDB.xlsx
+++ b/Assets/Resources/DataBase/Review Data/ReviewDB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Review Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5083B132-3A1B-467A-A9E0-6C44B51ED86F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E454F0-3161-4F6F-B250-56DB6326846E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,10 +87,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"진상의 정석이 있어도 진상 대응은 최악"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"너무 시끄럽고 무서워요..관리도 안하는 주유소"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -184,6 +180,10 @@
   </si>
   <si>
     <t>9만원에 가득채웠지만 또가고 싶은 GGM주유소 입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"진상 대응이 너무 아쉬움 너무 답답합니다."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -590,10 +590,10 @@
         <v>12</v>
       </c>
       <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
         <v>18</v>
-      </c>
-      <c r="E1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
@@ -604,13 +604,13 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
@@ -621,7 +621,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>13</v>
@@ -635,13 +635,13 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
         <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
@@ -652,10 +652,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
@@ -666,10 +666,10 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
@@ -680,13 +680,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
@@ -697,10 +697,10 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
@@ -711,13 +711,13 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
@@ -728,10 +728,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
@@ -745,7 +745,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
@@ -756,10 +756,10 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataBase/Review Data/ReviewDB.xlsx
+++ b/Assets/Resources/DataBase/Review Data/ReviewDB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Review Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E454F0-3161-4F6F-B250-56DB6326846E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70787E58-D6D6-48CE-A894-6F1CA3B04886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReviewSheet" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,22 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>마이클</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>잭슨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>빌리진</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NotMyLove</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>contentUp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -184,6 +168,194 @@
   </si>
   <si>
     <t>"진상 대응이 너무 아쉬움 너무 답답합니다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마이쿨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박철민</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박민철</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박민철</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지태환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박민성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최정우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정지한</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤도원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김용민</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김도현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전창준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남기태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한재훈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김민(2학년)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조한결</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한춘배</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김시원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안혁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예루</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>변지호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백범직</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정현진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정석주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정한결</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이훈성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>딩고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박태윤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박지민</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김희진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김민준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아미르</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유현우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우성태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박병건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김태준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신동완</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유태현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이윤담</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오도경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤이상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김동선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍지후(A)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍지후(B)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -587,13 +759,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
@@ -604,13 +776,13 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
@@ -621,10 +793,10 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
@@ -635,13 +807,13 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
@@ -652,10 +824,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
@@ -666,10 +838,10 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
@@ -680,13 +852,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
@@ -697,10 +869,10 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
@@ -711,13 +883,13 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
@@ -728,10 +900,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
@@ -745,7 +917,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
@@ -756,10 +928,10 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -770,7 +942,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A51"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
@@ -790,22 +962,242 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataBase/Review Data/ReviewDB.xlsx
+++ b/Assets/Resources/DataBase/Review Data/ReviewDB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Review Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70787E58-D6D6-48CE-A894-6F1CA3B04886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62604440-F2F2-427A-9AE2-EAA9B6B11DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="83">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -356,6 +356,10 @@
   </si>
   <si>
     <t>홍지후(B)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오도경</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -942,7 +946,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A51"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
@@ -1200,6 +1204,11 @@
         <v>81</v>
       </c>
     </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
